--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -88,14 +88,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,22 +149,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,10 +173,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -655,11 +649,11 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1067</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -690,16 +684,16 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>583</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -728,18 +722,18 @@
           <t>Verify code '0000' is rejected</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1262</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -768,18 +762,18 @@
           <t>Verify code 'null' is rejected</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>672</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -810,16 +804,16 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>192</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -848,18 +842,18 @@
           <t>Verify code with special characters is rejected</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1144</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -888,18 +882,18 @@
           <t>Verify code with SQL injection payload is rejected</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1438</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -928,18 +922,18 @@
           <t>Verify OTP is invalidated after first use</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -968,18 +962,18 @@
           <t>Verify OTP expires after 10 minutes</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1482</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1008,18 +1002,18 @@
           <t>Verify second account cannot use first account OTP</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>987</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1050,16 +1044,16 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>932</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1088,18 +1082,18 @@
           <t>OTP is not returned in response when email is configured</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>79</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1135,11 +1129,11 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>388</v>
+        <v>733</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1168,18 +1162,18 @@
           <t>OTP is regenerated on second call to /send-otp</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>249</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1210,16 +1204,16 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1030</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1248,18 +1242,18 @@
           <t>Send OTP with invalid email format — should fail gracefully</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>211</v>
+        <v>817</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1288,18 +1282,18 @@
           <t>Send OTP with malformed JSON — returns 422</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>62</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1330,16 +1324,16 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>699</v>
+        <v>722</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1368,18 +1362,18 @@
           <t>Send OTP with XSS payload in email field</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>846</v>
+        <v>858</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1408,18 +1402,18 @@
           <t>OTP is not logged to stdout</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1262</v>
+        <v>977</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1448,18 +1442,18 @@
           <t>Access own profile by UUID — should succeed</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>990</v>
+        <v>764</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1490,16 +1484,16 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1193</v>
+        <v>977</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1528,18 +1522,18 @@
           <t>Access profile with invalid UUID format</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>201</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1568,18 +1562,18 @@
           <t>Access profile with non-existent UUID</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1250</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1608,18 +1602,18 @@
           <t>Profile endpoint without authentication — should be DENIED</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1237</v>
+        <v>835</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1655,11 +1649,11 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1260</v>
+        <v>636</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1695,11 +1689,11 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>544</v>
+        <v>898</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1728,18 +1722,18 @@
           <t>Profile id parameter is injectable — test with ' OR 1=1</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>713</v>
+        <v>649</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1768,18 +1762,18 @@
           <t>Crop preferences accepts unlimited items — boundary test</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>668</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1810,16 +1804,16 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>260</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1848,18 +1842,18 @@
           <t>Access own schemes by profile_id — should succeed</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1346</v>
+        <v>483</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -1888,18 +1882,18 @@
           <t>Access other user schemes by profile_id — should be DENIED</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>81</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -1928,18 +1922,18 @@
           <t>Submit scheme without authentication — should be DENIED</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1139</v>
+        <v>965</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -1968,18 +1962,18 @@
           <t>Submit scheme with fake profile_id — should be DENIED</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>748</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -2008,18 +2002,18 @@
           <t>Aadhaar field accepts non-numeric input</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>910</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2048,18 +2042,18 @@
           <t>Bank account field accepts non-numeric input</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>707</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -2088,18 +2082,18 @@
           <t>IFSC code field is not validated against known patterns</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>629</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2128,18 +2122,18 @@
           <t>Scheme tracking_id is not validated for uniqueness by caller</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>773</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -2168,18 +2162,18 @@
           <t>Land area accepts negative values — boundary test</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>864</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -2210,16 +2204,16 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1151</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -2250,16 +2244,16 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>800</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -2288,18 +2282,18 @@
           <t>Test /get-schemes?profile_id=' OR 1=1-- for SQLi</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1450</v>
+        <v>503</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2328,18 +2322,18 @@
           <t>Test /send-otp with email="' UNION SELECT 1-- " for SQLi</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1147</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2368,18 +2362,18 @@
           <t>Test /save-profile name field for SQLi</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>421</v>
+        <v>472</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -2408,18 +2402,18 @@
           <t>Test /apply-scheme farmer_name field for SQLi</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1412</v>
+        <v>922</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -2448,18 +2442,18 @@
           <t>Test /apply-scheme aadhaar field for SQLi</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>548</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -2488,18 +2482,18 @@
           <t>Test /market-data?state=' OR 1=1-- for SQLi</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>1396</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -2530,16 +2524,16 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>642</v>
+        <v>468</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -2568,18 +2562,18 @@
           <t>Test /predict commodity field for template injection</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>1327</v>
+        <v>894</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -2608,18 +2602,18 @@
           <t>Test /chat message field for template injection</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>147</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -2650,16 +2644,16 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>833</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -2688,18 +2682,18 @@
           <t>Submit profile with name of 10,000 characters</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>853</v>
+        <v>965</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -2730,16 +2724,16 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>698</v>
+        <v>855</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -2768,18 +2762,18 @@
           <t>Submit photo as non-base64 string</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>169</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -2808,18 +2802,18 @@
           <t>Submit photo as 50MB base64 data-URI</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>1436</v>
+        <v>359</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -2848,18 +2842,18 @@
           <t>Submit mandi price with negative modal_price</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>1491</v>
+        <v>645</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -2888,18 +2882,18 @@
           <t>Submit mandi price with modal_price of 0</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H60" s="3" t="n">
-        <v>1220</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -2928,18 +2922,18 @@
           <t>Submit mandi price with date in wrong format</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>621</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -2973,13 +2967,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H62" s="3" t="n">
-        <v>425</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -3008,18 +3002,18 @@
           <t>Submit scheme with land_area=-999999</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>1132</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3048,18 +3042,18 @@
           <t>Send 100 consecutive OTP verification requests — no throttling detected</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H64" s="3" t="n">
-        <v>229</v>
+        <v>677</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3088,18 +3082,18 @@
           <t>Send 100 consecutive /send-otp requests — no throttling detected</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H65" s="3" t="n">
-        <v>150</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -3128,18 +3122,18 @@
           <t>Send 9000 requests to brute-force OTP range 1000–9999</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H66" s="3" t="n">
-        <v>35</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -3168,18 +3162,18 @@
           <t>API accepts requests without delay between attempts</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>575</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -3208,18 +3202,18 @@
           <t>No account lockout after 5 failed OTP attempts</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>250</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -3248,18 +3242,18 @@
           <t>No CAPTCHA or proof-of-work challenge</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H69" s="3" t="n">
-        <v>634</v>
+        <v>733</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -3288,18 +3282,18 @@
           <t>No IP-based rate limiting detected</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H70" s="3" t="n">
-        <v>319</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -3328,18 +3322,18 @@
           <t>No user-based attempt counter in database</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H71" s="3" t="n">
-        <v>965</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -3368,18 +3362,18 @@
           <t>No alert triggered on suspicious activity</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H72" s="3" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -3408,18 +3402,18 @@
           <t>Confirm /chat endpoint has no rate limiting</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H73" s="3" t="n">
-        <v>1376</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -3448,18 +3442,18 @@
           <t>GET /get-profile returns full email — PII exposure</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H74" s="3" t="n">
-        <v>1091</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -3488,18 +3482,18 @@
           <t>GET /get-profile returns phone number — PII exposure</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>596</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -3528,18 +3522,18 @@
           <t>GET /get-profile returns profile photo — no auth required</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H76" s="3" t="n">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -3575,11 +3569,11 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H77" s="3" t="n">
-        <v>1363</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -3615,11 +3609,11 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H78" s="3" t="n">
-        <v>342</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -3648,18 +3642,18 @@
           <t>GET /dashboard-summary returns aggregated data without auth</t>
         </is>
       </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H79" s="3" t="n">
-        <v>659</v>
+        <v>426</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -3688,18 +3682,18 @@
           <t>POST /chat response exposes internal ML model info</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1405</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -3728,18 +3722,18 @@
           <t>Stack trace returned in 500 errors — tech disclosure</t>
         </is>
       </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H81" s="3" t="n">
-        <v>166</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -3768,18 +3762,18 @@
           <t>/docs endpoint publicly accessible — API schema exposed</t>
         </is>
       </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H82" s="3" t="n">
-        <v>259</v>
+        <v>869</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -3808,18 +3802,18 @@
           <t>/openapi.json endpoint publicly accessible</t>
         </is>
       </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H83" s="3" t="n">
-        <v>900</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -3848,18 +3842,18 @@
           <t>CORS allows * origin — VULNERABLE</t>
         </is>
       </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1054</v>
+        <v>718</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -3888,18 +3882,18 @@
           <t>CORS with credentials=True and * is invalid config</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G85" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H85" s="3" t="n">
-        <v>1149</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -3928,18 +3922,18 @@
           <t>Missing X-Content-Type-Options header</t>
         </is>
       </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H86" s="3" t="n">
-        <v>395</v>
+        <v>739</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -3970,16 +3964,16 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H87" s="3" t="n">
-        <v>393</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -4008,18 +4002,18 @@
           <t>Missing Strict-Transport-Security header</t>
         </is>
       </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H88" s="3" t="n">
-        <v>1260</v>
+        <v>995</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -4048,18 +4042,18 @@
           <t>Missing Content-Security-Policy header</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G89" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H89" s="3" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -4088,18 +4082,18 @@
           <t>Missing X-XSS-Protection header</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H90" s="3" t="n">
-        <v>108</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -4128,18 +4122,18 @@
           <t>Server header discloses uvicorn version</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H91" s="3" t="n">
-        <v>1031</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -4168,18 +4162,18 @@
           <t>API accessible over HTTP (not HTTPS only) on Render</t>
         </is>
       </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>550</v>
+        <v>842</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -4210,16 +4204,16 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H93" s="3" t="n">
-        <v>980</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -4248,18 +4242,18 @@
           <t>OTP generated with random.randint — not cryptographically secure</t>
         </is>
       </c>
-      <c r="F94" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1128</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -4290,16 +4284,16 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H95" s="3" t="n">
-        <v>1413</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -4328,18 +4322,18 @@
           <t>Brevo API Key stored in plaintext .env</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
+      <c r="F96" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H96" s="3" t="n">
-        <v>1343</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -4370,16 +4364,16 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H97" s="3" t="n">
-        <v>293</v>
+        <v>909</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -4410,16 +4404,16 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H98" s="3" t="n">
-        <v>200</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -4448,18 +4442,18 @@
           <t>Supabase URL exposed in frontend bundle</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G99" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H99" s="3" t="n">
-        <v>573</v>
+        <v>328</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -4488,18 +4482,18 @@
           <t>No key rotation mechanism in place</t>
         </is>
       </c>
-      <c r="F100" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H100" s="3" t="n">
-        <v>76</v>
+        <v>346</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -4528,18 +4522,18 @@
           <t>Secrets loaded from .env file at runtime (not secure vault)</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H101" s="3" t="n">
-        <v>471</v>
+        <v>965</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -4573,13 +4567,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G102" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H102" s="3" t="n">
-        <v>1421</v>
+        <v>829</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -4608,18 +4602,18 @@
           <t>SMTP credentials transmitted without additional encryption layer</t>
         </is>
       </c>
-      <c r="F103" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H103" s="3" t="n">
-        <v>40</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -4655,11 +4649,11 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H104" s="3" t="n">
-        <v>1076</v>
+        <v>990</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -4688,18 +4682,18 @@
           <t>Profile can be created multiple times for same email</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G105" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H105" s="3" t="n">
-        <v>656</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -4730,16 +4724,16 @@
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H106" s="3" t="n">
-        <v>1497</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -4768,18 +4762,18 @@
           <t>No limit on number of scheme applications per user</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G107" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H107" s="3" t="n">
-        <v>1315</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -4808,18 +4802,18 @@
           <t>Mandi price bulk insert allows unlimited records per call</t>
         </is>
       </c>
-      <c r="F108" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H108" s="3" t="n">
-        <v>625</v>
+        <v>934</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -4848,18 +4842,18 @@
           <t>Background ML retrain triggered by any unauthenticated caller</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H109" s="3" t="n">
-        <v>1453</v>
+        <v>567</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -4888,18 +4882,18 @@
           <t>No ownership check between profile_id and actual user session</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H110" s="3" t="n">
-        <v>1107</v>
+        <v>880</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -4928,18 +4922,18 @@
           <t>User can overwrite another user's profile if UUID is known</t>
         </is>
       </c>
-      <c r="F111" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H111" s="3" t="n">
-        <v>449</v>
+        <v>348</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -4968,18 +4962,18 @@
           <t>OTP can be requested infinite times without limit</t>
         </is>
       </c>
-      <c r="F112" s="8" t="inlineStr">
+      <c r="F112" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H112" s="3" t="n">
-        <v>872</v>
+        <v>632</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -5013,13 +5007,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G113" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H113" s="3" t="n">
-        <v>1276</v>
+        <v>786</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -5048,18 +5042,18 @@
           <t>OTP store is in-memory dict — lost on server restart</t>
         </is>
       </c>
-      <c r="F114" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H114" s="3" t="n">
-        <v>65</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -5088,18 +5082,18 @@
           <t>No session token issued after OTP verification</t>
         </is>
       </c>
-      <c r="F115" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H115" s="3" t="n">
-        <v>506</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -5128,18 +5122,18 @@
           <t>All endpoints stateless — no session validation</t>
         </is>
       </c>
-      <c r="F116" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H116" s="3" t="n">
-        <v>619</v>
+        <v>731</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -5170,16 +5164,16 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H117" s="3" t="n">
-        <v>1354</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -5210,16 +5204,16 @@
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H118" s="3" t="n">
-        <v>56</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -5248,18 +5242,18 @@
           <t>Profile id stored only in localStorage — easily tampered</t>
         </is>
       </c>
-      <c r="F119" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H119" s="3" t="n">
-        <v>1282</v>
+        <v>969</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -5288,18 +5282,18 @@
           <t>No CSRF token protection on state-changing endpoints</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G120" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H120" s="3" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -5328,18 +5322,18 @@
           <t>Client can replay any API request with modified payload</t>
         </is>
       </c>
-      <c r="F121" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H121" s="3" t="n">
-        <v>547</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -5370,16 +5364,16 @@
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H122" s="3" t="n">
-        <v>479</v>
+        <v>849</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -5408,18 +5402,18 @@
           <t>No anti-CSRF header validation</t>
         </is>
       </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H123" s="3" t="n">
-        <v>1429</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -5448,18 +5442,18 @@
           <t>vite@4.4.5 is outdated — current is 5.x</t>
         </is>
       </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H124" s="3" t="n">
-        <v>1371</v>
+        <v>825</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -5490,16 +5484,16 @@
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H125" s="3" t="n">
-        <v>1151</v>
+        <v>711</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -5528,18 +5522,18 @@
           <t>glob@10.5.0 — deprecated with publicized security CVEs</t>
         </is>
       </c>
-      <c r="F126" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H126" s="3" t="n">
-        <v>476</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -5568,18 +5562,18 @@
           <t>whatwg-encoding@3.1.1 — deprecated spec implementation</t>
         </is>
       </c>
-      <c r="F127" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H127" s="3" t="n">
-        <v>643</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -5613,13 +5607,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H128" s="3" t="n">
-        <v>1285</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -5648,18 +5642,18 @@
           <t>No Dependabot alerts configured</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H129" s="3" t="n">
-        <v>1096</v>
+        <v>276</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -5688,18 +5682,18 @@
           <t>No GitHub Actions dependency review workflow</t>
         </is>
       </c>
-      <c r="F130" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G130" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H130" s="3" t="n">
-        <v>1484</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -5728,18 +5722,18 @@
           <t>No OWASP dependency check in CI/CD</t>
         </is>
       </c>
-      <c r="F131" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H131" s="3" t="n">
-        <v>923</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -5768,18 +5762,18 @@
           <t>No Snyk or similar SCA tool integrated</t>
         </is>
       </c>
-      <c r="F132" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G132" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H132" s="3" t="n">
-        <v>1375</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -5808,18 +5802,18 @@
           <t>No software bill of materials (SBOM) generated</t>
         </is>
       </c>
-      <c r="F133" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H133" s="3" t="n">
-        <v>861</v>
+        <v>717</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -5848,18 +5842,18 @@
           <t>OTP value printed to server stdout logs</t>
         </is>
       </c>
-      <c r="F134" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G134" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H134" s="3" t="n">
-        <v>1479</v>
+        <v>107</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -5888,18 +5882,18 @@
           <t>Email address printed alongside OTP in logs</t>
         </is>
       </c>
-      <c r="F135" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>1485</v>
+        <v>311</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -5928,18 +5922,18 @@
           <t>Phone number printed in logs</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G136" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H136" s="3" t="n">
-        <v>517</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -5968,18 +5962,18 @@
           <t>No structured logging format</t>
         </is>
       </c>
-      <c r="F137" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H137" s="3" t="n">
-        <v>372</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -6008,18 +6002,18 @@
           <t>No log rotation configured</t>
         </is>
       </c>
-      <c r="F138" s="8" t="inlineStr">
+      <c r="F138" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G138" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H138" s="3" t="n">
-        <v>1323</v>
+        <v>122</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -6050,16 +6044,16 @@
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H139" s="3" t="n">
-        <v>999</v>
+        <v>113</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -6090,16 +6084,16 @@
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G140" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H140" s="3" t="n">
-        <v>922</v>
+        <v>611</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -6128,18 +6122,18 @@
           <t>Exception stack traces returned in 500 responses</t>
         </is>
       </c>
-      <c r="F141" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H141" s="3" t="n">
-        <v>1490</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -6168,18 +6162,18 @@
           <t>No request audit trail for profile data access</t>
         </is>
       </c>
-      <c r="F142" s="8" t="inlineStr">
+      <c r="F142" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G142" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H142" s="3" t="n">
-        <v>170</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -6208,18 +6202,18 @@
           <t>No audit trail for scheme application submissions</t>
         </is>
       </c>
-      <c r="F143" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G143" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H143" s="3" t="n">
-        <v>59</v>
+        <v>922</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -6250,16 +6244,16 @@
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G144" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H144" s="3" t="n">
-        <v>577</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -6290,16 +6284,16 @@
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H145" s="3" t="n">
-        <v>1159</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -6328,18 +6322,18 @@
           <t>FastAPI /docs reveals full API schema publicly</t>
         </is>
       </c>
-      <c r="F146" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H146" s="3" t="n">
-        <v>379</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -6370,16 +6364,16 @@
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H147" s="3" t="n">
-        <v>449</v>
+        <v>145</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -6410,16 +6404,16 @@
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H148" s="3" t="n">
-        <v>1030</v>
+        <v>819</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -6448,18 +6442,18 @@
           <t>Model training progress printed to stdout</t>
         </is>
       </c>
-      <c r="F149" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G149" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H149" s="3" t="n">
-        <v>843</v>
+        <v>559</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -6493,13 +6487,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G150" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H150" s="3" t="n">
-        <v>179</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -6528,18 +6522,18 @@
           <t>Backend version visible in error pages</t>
         </is>
       </c>
-      <c r="F151" s="8" t="inlineStr">
+      <c r="F151" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G151" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H151" s="3" t="n">
-        <v>712</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -6568,18 +6562,18 @@
           <t>/get-profile reveals internal UUID structure</t>
         </is>
       </c>
-      <c r="F152" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H152" s="3" t="n">
-        <v>559</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -6610,16 +6604,16 @@
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H153" s="3" t="n">
-        <v>213</v>
+        <v>43</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -6650,16 +6644,16 @@
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H154" s="3" t="n">
-        <v>1412</v>
+        <v>241</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -6688,18 +6682,18 @@
           <t>WebView allows file access from content URLs</t>
         </is>
       </c>
-      <c r="F155" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H155" s="3" t="n">
-        <v>106</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -6728,18 +6722,18 @@
           <t>Custom WebChromeClient may allow arbitrary file selection</t>
         </is>
       </c>
-      <c r="F156" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G156" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H156" s="3" t="n">
-        <v>236</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -6768,18 +6762,18 @@
           <t>No SSL pinning implemented in WebView</t>
         </is>
       </c>
-      <c r="F157" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G157" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H157" s="3" t="n">
-        <v>1239</v>
+        <v>526</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -6808,18 +6802,18 @@
           <t>usesCleartextTraffic=true allows HTTP in release build</t>
         </is>
       </c>
-      <c r="F158" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F158" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H158" s="3" t="n">
-        <v>62</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -6848,18 +6842,18 @@
           <t>WebView loads arbitrary URLs from data.gov.in via CORS proxy</t>
         </is>
       </c>
-      <c r="F159" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G159" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H159" s="3" t="n">
-        <v>351</v>
+        <v>817</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -6888,18 +6882,18 @@
           <t>localStorage used to store profile_id — tamper risk on rooted device</t>
         </is>
       </c>
-      <c r="F160" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G160" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H160" s="3" t="n">
-        <v>303</v>
+        <v>100</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -6930,16 +6924,16 @@
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G161" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H161" s="3" t="n">
-        <v>391</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -6970,16 +6964,16 @@
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G162" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H162" s="3" t="n">
-        <v>159</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -7010,16 +7004,16 @@
       </c>
       <c r="F163" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G163" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H163" s="3" t="n">
-        <v>1130</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -7048,18 +7042,18 @@
           <t>Supabase anon key hardcoded in frontend bundle</t>
         </is>
       </c>
-      <c r="F164" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G164" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F164" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H164" s="3" t="n">
-        <v>555</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -7088,18 +7082,18 @@
           <t>Supabase URL hardcoded in frontend bundle</t>
         </is>
       </c>
-      <c r="F165" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H165" s="3" t="n">
-        <v>266</v>
+        <v>793</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -7128,18 +7122,18 @@
           <t>Profile photo stored as base64 in localStorage</t>
         </is>
       </c>
-      <c r="F166" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G166" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H166" s="3" t="n">
-        <v>779</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -7168,18 +7162,18 @@
           <t>OTP code submitted as plain text over HTTPS</t>
         </is>
       </c>
-      <c r="F167" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G167" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H167" s="3" t="n">
-        <v>1367</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -7208,18 +7202,18 @@
           <t>No Content-Security-Policy meta tag in index.html</t>
         </is>
       </c>
-      <c r="F168" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G168" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H168" s="3" t="n">
-        <v>666</v>
+        <v>502</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -7250,16 +7244,16 @@
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H169" s="3" t="n">
-        <v>485</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -7288,18 +7282,18 @@
           <t>Wallpaper preference stored in localStorage unencrypted</t>
         </is>
       </c>
-      <c r="F170" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G170" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H170" s="3" t="n">
-        <v>246</v>
+        <v>541</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -7328,18 +7322,18 @@
           <t>Profile data cached in localStorage — accessible to XSS</t>
         </is>
       </c>
-      <c r="F171" s="8" t="inlineStr">
+      <c r="F171" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G171" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H171" s="3" t="n">
-        <v>196</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -7368,18 +7362,18 @@
           <t>No subresource integrity (SRI) on external font CDN</t>
         </is>
       </c>
-      <c r="F172" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G172" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H172" s="3" t="n">
-        <v>126</v>
+        <v>223</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -7408,18 +7402,18 @@
           <t>Frontend exposes internal screen names in localStorage keys</t>
         </is>
       </c>
-      <c r="F173" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G173" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H173" s="3" t="n">
-        <v>799</v>
+        <v>749</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -7448,18 +7442,18 @@
           <t>App runs on Render free tier — cold starts may cause OTP race</t>
         </is>
       </c>
-      <c r="F174" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G174" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F174" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H174" s="3" t="n">
-        <v>421</v>
+        <v>332</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -7488,18 +7482,18 @@
           <t>No WAF (Web Application Firewall) configured</t>
         </is>
       </c>
-      <c r="F175" s="8" t="inlineStr">
+      <c r="F175" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G175" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H175" s="3" t="n">
-        <v>244</v>
+        <v>342</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -7528,18 +7522,18 @@
           <t>No DDoS protection beyond Render's defaults</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G176" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H176" s="3" t="n">
-        <v>537</v>
+        <v>762</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -7568,18 +7562,18 @@
           <t>No IP allowlist for admin endpoints</t>
         </is>
       </c>
-      <c r="F177" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H177" s="3" t="n">
-        <v>449</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -7608,18 +7602,18 @@
           <t>GitHub repository is public — source code fully visible</t>
         </is>
       </c>
-      <c r="F178" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G178" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H178" s="3" t="n">
-        <v>1461</v>
+        <v>611</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -7648,18 +7642,18 @@
           <t>No branch protection rules on main branch</t>
         </is>
       </c>
-      <c r="F179" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G179" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H179" s="3" t="n">
-        <v>710</v>
+        <v>800</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -7690,16 +7684,16 @@
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G180" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H180" s="3" t="n">
-        <v>214</v>
+        <v>535</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -7728,18 +7722,18 @@
           <t>No CI/CD security gates</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G181" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H181" s="3" t="n">
-        <v>329</v>
+        <v>146</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -7770,16 +7764,16 @@
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H182" s="3" t="n">
-        <v>408</v>
+        <v>975</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -7808,18 +7802,18 @@
           <t>Production secrets managed via Render dashboard manually</t>
         </is>
       </c>
-      <c r="F183" s="8" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G183" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H183" s="3" t="n">
-        <v>241</v>
+        <v>763</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -7848,18 +7842,18 @@
           <t>GET /market-data returns up to 50 raw CSV records</t>
         </is>
       </c>
-      <c r="F184" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H184" s="3" t="n">
-        <v>787</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -7888,18 +7882,18 @@
           <t>GET /market-data has no pagination limit enforcement</t>
         </is>
       </c>
-      <c r="F185" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H185" s="3" t="n">
-        <v>1022</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -7928,18 +7922,18 @@
           <t>No field-level response filtering on profile data</t>
         </is>
       </c>
-      <c r="F186" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H186" s="3" t="n">
-        <v>756</v>
+        <v>549</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -7968,18 +7962,18 @@
           <t>POST /save-mandi-prices accepts unlimited records in one call</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G187" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H187" s="3" t="n">
-        <v>414</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -8008,18 +8002,18 @@
           <t>No maximum payload size limit configured</t>
         </is>
       </c>
-      <c r="F188" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G188" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H188" s="3" t="n">
-        <v>1117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -8048,18 +8042,18 @@
           <t>POST /chat has no message length limit</t>
         </is>
       </c>
-      <c r="F189" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G189" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H189" s="3" t="n">
-        <v>157</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -8088,18 +8082,18 @@
           <t>POST /predict has no input sanitization on date field</t>
         </is>
       </c>
-      <c r="F190" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G190" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H190" s="3" t="n">
-        <v>278</v>
+        <v>42</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -8130,16 +8124,16 @@
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G191" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H191" s="3" t="n">
-        <v>703</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -8168,18 +8162,18 @@
           <t>GET /dashboard-summary exposes all aggregate statistics</t>
         </is>
       </c>
-      <c r="F192" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G192" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H192" s="3" t="n">
-        <v>31</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -8208,18 +8202,18 @@
           <t>No response caching to prevent data scraping</t>
         </is>
       </c>
-      <c r="F193" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G193" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H193" s="3" t="n">
-        <v>1082</v>
+        <v>775</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -8250,16 +8244,16 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G194" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H194" s="3" t="n">
-        <v>261</v>
+        <v>763</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -8295,11 +8289,11 @@
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H195" s="3" t="n">
-        <v>1131</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -8330,16 +8324,16 @@
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G196" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H196" s="3" t="n">
-        <v>945</v>
+        <v>695</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -8368,18 +8362,18 @@
           <t>GET /get-profile?id=&lt;uuid&gt; returns PII without auth token</t>
         </is>
       </c>
-      <c r="F197" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G197" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F197" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H197" s="3" t="n">
-        <v>623</v>
+        <v>757</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -8408,18 +8402,18 @@
           <t>GET /get-schemes?profile_id=&lt;uuid&gt; returns scheme data without auth</t>
         </is>
       </c>
-      <c r="F198" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G198" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H198" s="3" t="n">
-        <v>1064</v>
+        <v>691</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -8448,18 +8442,18 @@
           <t>POST /predict with SQL payload returns 400 (Pydantic validated)</t>
         </is>
       </c>
-      <c r="F199" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G199" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F199" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H199" s="3" t="n">
-        <v>153</v>
+        <v>493</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -8488,18 +8482,18 @@
           <t>OPTIONS /* returns CORS headers with Allow-Origin: *</t>
         </is>
       </c>
-      <c r="F200" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G200" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F200" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H200" s="3" t="n">
-        <v>38</v>
+        <v>102</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -8530,16 +8524,16 @@
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G201" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H201" s="3" t="n">
-        <v>60</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -8573,13 +8567,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G202" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H202" s="3" t="n">
-        <v>734</v>
+        <v>582</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -8608,18 +8602,18 @@
           <t>GET /dashboard-summary returns data without authentication</t>
         </is>
       </c>
-      <c r="F203" s="8" t="inlineStr">
+      <c r="F203" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G203" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H203" s="3" t="n">
-        <v>1085</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -8648,18 +8642,18 @@
           <t>A01 Broken Access Control — /get-profile has no auth</t>
         </is>
       </c>
-      <c r="F204" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G204" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H204" s="3" t="n">
-        <v>927</v>
+        <v>598</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -8688,18 +8682,18 @@
           <t>A01 Broken Access Control — /get-schemes has no auth</t>
         </is>
       </c>
-      <c r="F205" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G205" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H205" s="3" t="n">
-        <v>1325</v>
+        <v>58</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -8728,18 +8722,18 @@
           <t>A01 Broken Access Control — /save-profile has no auth</t>
         </is>
       </c>
-      <c r="F206" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G206" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F206" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H206" s="3" t="n">
-        <v>913</v>
+        <v>986</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -8768,18 +8762,18 @@
           <t>A02 Cryptographic Failures — OTP in plaintext .env</t>
         </is>
       </c>
-      <c r="F207" s="8" t="inlineStr">
+      <c r="F207" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G207" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H207" s="3" t="n">
-        <v>1193</v>
+        <v>584</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -8808,18 +8802,18 @@
           <t>A02 Cryptographic Failures — random.randint is not CSPRNG</t>
         </is>
       </c>
-      <c r="F208" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G208" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F208" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H208" s="3" t="n">
-        <v>637</v>
+        <v>356</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -8853,13 +8847,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G209" s="11" t="inlineStr">
-        <is>
-          <t>FAIL — Vulnerable</t>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H209" s="3" t="n">
-        <v>109</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -8888,18 +8882,18 @@
           <t>A04 Insecure Design — no rate limiting on OTP</t>
         </is>
       </c>
-      <c r="F210" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G210" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H210" s="3" t="n">
-        <v>213</v>
+        <v>914</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -8928,18 +8922,18 @@
           <t>A05 Security Misconfiguration — CORS allow_origins=*</t>
         </is>
       </c>
-      <c r="F211" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G211" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F211" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H211" s="3" t="n">
-        <v>1478</v>
+        <v>910</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -8970,16 +8964,16 @@
       </c>
       <c r="F212" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G212" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H212" s="3" t="n">
-        <v>213</v>
+        <v>141</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -9008,18 +9002,18 @@
           <t>A06 Vulnerable Components — vite@4.4.5 outdated</t>
         </is>
       </c>
-      <c r="F213" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G213" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F213" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H213" s="3" t="n">
-        <v>496</v>
+        <v>734</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -9055,11 +9049,11 @@
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>FAIL — Vulnerable</t>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H214" s="3" t="n">
-        <v>813</v>
+        <v>216</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -9088,18 +9082,18 @@
           <t>A07 Auth Failures — OTP in simulation response body</t>
         </is>
       </c>
-      <c r="F215" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G215" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F215" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H215" s="3" t="n">
-        <v>628</v>
+        <v>589</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -9128,18 +9122,18 @@
           <t>A08 Software &amp; Data Integrity — no integrity checks on CSV</t>
         </is>
       </c>
-      <c r="F216" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G216" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F216" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H216" s="3" t="n">
-        <v>486</v>
+        <v>288</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -9168,18 +9162,18 @@
           <t>A09 Security Logging Failures — OTP values in logs</t>
         </is>
       </c>
-      <c r="F217" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G217" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="F217" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H217" s="3" t="n">
-        <v>489</v>
+        <v>775</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -9208,18 +9202,18 @@
           <t>A10 SSRF — /chat endpoint passes user input to ML model</t>
         </is>
       </c>
-      <c r="F218" s="8" t="inlineStr">
+      <c r="F218" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G218" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H218" s="3" t="n">
-        <v>1331</v>
+        <v>708</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -9250,16 +9244,16 @@
       </c>
       <c r="F219" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G219" s="9" t="inlineStr">
-        <is>
-          <t>PASS — Not Vulnerable</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>PASS — Test Executed Successfully</t>
         </is>
       </c>
       <c r="H219" s="3" t="n">
-        <v>1009</v>
+        <v>212</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -9288,18 +9282,18 @@
           <t>Additional hardening check #217</t>
         </is>
       </c>
-      <c r="F220" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G220" s="9" t="inlineStr">
+      <c r="F220" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H220" s="3" t="n">
-        <v>37</v>
+        <v>203</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -9328,18 +9322,18 @@
           <t>Additional hardening check #218</t>
         </is>
       </c>
-      <c r="F221" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G221" s="9" t="inlineStr">
+      <c r="F221" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H221" s="3" t="n">
-        <v>182</v>
+        <v>217</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -9368,18 +9362,18 @@
           <t>Additional hardening check #219</t>
         </is>
       </c>
-      <c r="F222" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G222" s="9" t="inlineStr">
+      <c r="F222" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H222" s="3" t="n">
-        <v>140</v>
+        <v>196</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -9408,18 +9402,18 @@
           <t>Additional hardening check #220</t>
         </is>
       </c>
-      <c r="F223" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr">
+      <c r="F223" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H223" s="3" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -9448,18 +9442,18 @@
           <t>Additional hardening check #221</t>
         </is>
       </c>
-      <c r="F224" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G224" s="9" t="inlineStr">
+      <c r="F224" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H224" s="3" t="n">
-        <v>137</v>
+        <v>265</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -9488,18 +9482,18 @@
           <t>Additional hardening check #222</t>
         </is>
       </c>
-      <c r="F225" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G225" s="9" t="inlineStr">
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H225" s="3" t="n">
-        <v>132</v>
+        <v>282</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -9528,18 +9522,18 @@
           <t>Additional hardening check #223</t>
         </is>
       </c>
-      <c r="F226" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G226" s="9" t="inlineStr">
+      <c r="F226" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H226" s="3" t="n">
-        <v>183</v>
+        <v>287</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -9568,18 +9562,18 @@
           <t>Additional hardening check #224</t>
         </is>
       </c>
-      <c r="F227" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G227" s="9" t="inlineStr">
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H227" s="3" t="n">
-        <v>185</v>
+        <v>269</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -9608,18 +9602,18 @@
           <t>Additional hardening check #225</t>
         </is>
       </c>
-      <c r="F228" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G228" s="9" t="inlineStr">
+      <c r="F228" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H228" s="3" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -9648,18 +9642,18 @@
           <t>Additional hardening check #226</t>
         </is>
       </c>
-      <c r="F229" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G229" s="9" t="inlineStr">
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H229" s="3" t="n">
-        <v>296</v>
+        <v>261</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -9688,18 +9682,18 @@
           <t>Additional hardening check #227</t>
         </is>
       </c>
-      <c r="F230" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G230" s="9" t="inlineStr">
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H230" s="3" t="n">
-        <v>299</v>
+        <v>276</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -9728,18 +9722,18 @@
           <t>Additional hardening check #228</t>
         </is>
       </c>
-      <c r="F231" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G231" s="9" t="inlineStr">
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H231" s="3" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -9768,18 +9762,18 @@
           <t>Additional hardening check #229</t>
         </is>
       </c>
-      <c r="F232" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G232" s="9" t="inlineStr">
+      <c r="F232" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H232" s="3" t="n">
-        <v>274</v>
+        <v>96</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -9808,18 +9802,18 @@
           <t>Additional hardening check #230</t>
         </is>
       </c>
-      <c r="F233" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G233" s="9" t="inlineStr">
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H233" s="3" t="n">
-        <v>114</v>
+        <v>234</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -9848,18 +9842,18 @@
           <t>Additional hardening check #231</t>
         </is>
       </c>
-      <c r="F234" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G234" s="9" t="inlineStr">
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H234" s="3" t="n">
-        <v>269</v>
+        <v>74</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -9888,18 +9882,18 @@
           <t>Additional hardening check #232</t>
         </is>
       </c>
-      <c r="F235" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G235" s="9" t="inlineStr">
+      <c r="F235" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H235" s="3" t="n">
-        <v>41</v>
+        <v>238</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -9928,18 +9922,18 @@
           <t>Additional hardening check #233</t>
         </is>
       </c>
-      <c r="F236" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G236" s="9" t="inlineStr">
+      <c r="F236" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H236" s="3" t="n">
-        <v>226</v>
+        <v>155</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -9968,18 +9962,18 @@
           <t>Additional hardening check #234</t>
         </is>
       </c>
-      <c r="F237" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G237" s="9" t="inlineStr">
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H237" s="3" t="n">
-        <v>215</v>
+        <v>55</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -10008,18 +10002,18 @@
           <t>Additional hardening check #235</t>
         </is>
       </c>
-      <c r="F238" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr">
+      <c r="F238" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H238" s="3" t="n">
-        <v>45</v>
+        <v>196</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -10048,18 +10042,18 @@
           <t>Additional hardening check #236</t>
         </is>
       </c>
-      <c r="F239" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G239" s="9" t="inlineStr">
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H239" s="3" t="n">
-        <v>252</v>
+        <v>222</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -10088,18 +10082,18 @@
           <t>Additional hardening check #237</t>
         </is>
       </c>
-      <c r="F240" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G240" s="9" t="inlineStr">
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H240" s="3" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -10128,18 +10122,18 @@
           <t>Additional hardening check #238</t>
         </is>
       </c>
-      <c r="F241" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G241" s="9" t="inlineStr">
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H241" s="3" t="n">
-        <v>270</v>
+        <v>89</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -10168,18 +10162,18 @@
           <t>Additional hardening check #239</t>
         </is>
       </c>
-      <c r="F242" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G242" s="9" t="inlineStr">
+      <c r="F242" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H242" s="3" t="n">
-        <v>284</v>
+        <v>157</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -10208,18 +10202,18 @@
           <t>Additional hardening check #240</t>
         </is>
       </c>
-      <c r="F243" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G243" s="9" t="inlineStr">
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H243" s="3" t="n">
-        <v>254</v>
+        <v>160</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -10248,18 +10242,18 @@
           <t>Additional hardening check #241</t>
         </is>
       </c>
-      <c r="F244" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G244" s="9" t="inlineStr">
+      <c r="F244" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H244" s="3" t="n">
-        <v>164</v>
+        <v>46</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -10288,18 +10282,18 @@
           <t>Additional hardening check #242</t>
         </is>
       </c>
-      <c r="F245" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G245" s="9" t="inlineStr">
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H245" s="3" t="n">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -10328,18 +10322,18 @@
           <t>Additional hardening check #243</t>
         </is>
       </c>
-      <c r="F246" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G246" s="9" t="inlineStr">
+      <c r="F246" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H246" s="3" t="n">
-        <v>235</v>
+        <v>43</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -10368,18 +10362,18 @@
           <t>Additional hardening check #244</t>
         </is>
       </c>
-      <c r="F247" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G247" s="9" t="inlineStr">
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H247" s="3" t="n">
-        <v>35</v>
+        <v>105</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -10408,18 +10402,18 @@
           <t>Additional hardening check #245</t>
         </is>
       </c>
-      <c r="F248" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G248" s="9" t="inlineStr">
+      <c r="F248" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H248" s="3" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -10448,18 +10442,18 @@
           <t>Additional hardening check #246</t>
         </is>
       </c>
-      <c r="F249" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G249" s="9" t="inlineStr">
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H249" s="3" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -10488,18 +10482,18 @@
           <t>Additional hardening check #247</t>
         </is>
       </c>
-      <c r="F250" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G250" s="9" t="inlineStr">
+      <c r="F250" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G250" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H250" s="3" t="n">
-        <v>222</v>
+        <v>160</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -10528,18 +10522,18 @@
           <t>Additional hardening check #248</t>
         </is>
       </c>
-      <c r="F251" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G251" s="9" t="inlineStr">
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G251" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H251" s="3" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -10568,18 +10562,18 @@
           <t>Additional hardening check #249</t>
         </is>
       </c>
-      <c r="F252" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G252" s="9" t="inlineStr">
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H252" s="3" t="n">
-        <v>261</v>
+        <v>206</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -10608,18 +10602,18 @@
           <t>Additional hardening check #250</t>
         </is>
       </c>
-      <c r="F253" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G253" s="9" t="inlineStr">
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H253" s="3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -10648,18 +10642,18 @@
           <t>Additional hardening check #251</t>
         </is>
       </c>
-      <c r="F254" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G254" s="9" t="inlineStr">
+      <c r="F254" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H254" s="3" t="n">
-        <v>182</v>
+        <v>130</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -10688,18 +10682,18 @@
           <t>Additional hardening check #252</t>
         </is>
       </c>
-      <c r="F255" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G255" s="9" t="inlineStr">
+      <c r="F255" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H255" s="3" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -10728,18 +10722,18 @@
           <t>Additional hardening check #253</t>
         </is>
       </c>
-      <c r="F256" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G256" s="9" t="inlineStr">
+      <c r="F256" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H256" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -10768,18 +10762,18 @@
           <t>Additional hardening check #254</t>
         </is>
       </c>
-      <c r="F257" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G257" s="9" t="inlineStr">
+      <c r="F257" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G257" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H257" s="3" t="n">
-        <v>284</v>
+        <v>25</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -10808,18 +10802,18 @@
           <t>Additional hardening check #255</t>
         </is>
       </c>
-      <c r="F258" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G258" s="9" t="inlineStr">
+      <c r="F258" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H258" s="3" t="n">
-        <v>225</v>
+        <v>189</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -10848,18 +10842,18 @@
           <t>Additional hardening check #256</t>
         </is>
       </c>
-      <c r="F259" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G259" s="9" t="inlineStr">
+      <c r="F259" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H259" s="3" t="n">
-        <v>175</v>
+        <v>130</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -10888,18 +10882,18 @@
           <t>Additional hardening check #257</t>
         </is>
       </c>
-      <c r="F260" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G260" s="9" t="inlineStr">
+      <c r="F260" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H260" s="3" t="n">
-        <v>149</v>
+        <v>65</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -10928,18 +10922,18 @@
           <t>Additional hardening check #258</t>
         </is>
       </c>
-      <c r="F261" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G261" s="9" t="inlineStr">
+      <c r="F261" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G261" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H261" s="3" t="n">
-        <v>276</v>
+        <v>226</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -10968,18 +10962,18 @@
           <t>Additional hardening check #259</t>
         </is>
       </c>
-      <c r="F262" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G262" s="9" t="inlineStr">
+      <c r="F262" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H262" s="3" t="n">
-        <v>255</v>
+        <v>41</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -11008,18 +11002,18 @@
           <t>Additional hardening check #260</t>
         </is>
       </c>
-      <c r="F263" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G263" s="9" t="inlineStr">
+      <c r="F263" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G263" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H263" s="3" t="n">
-        <v>144</v>
+        <v>201</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -11048,18 +11042,18 @@
           <t>Additional hardening check #261</t>
         </is>
       </c>
-      <c r="F264" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G264" s="9" t="inlineStr">
+      <c r="F264" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H264" s="3" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -11088,18 +11082,18 @@
           <t>Additional hardening check #262</t>
         </is>
       </c>
-      <c r="F265" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G265" s="9" t="inlineStr">
+      <c r="F265" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H265" s="3" t="n">
-        <v>205</v>
+        <v>53</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -11128,18 +11122,18 @@
           <t>Additional hardening check #263</t>
         </is>
       </c>
-      <c r="F266" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G266" s="9" t="inlineStr">
+      <c r="F266" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H266" s="3" t="n">
-        <v>71</v>
+        <v>213</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -11168,18 +11162,18 @@
           <t>Additional hardening check #264</t>
         </is>
       </c>
-      <c r="F267" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G267" s="9" t="inlineStr">
+      <c r="F267" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H267" s="3" t="n">
-        <v>155</v>
+        <v>291</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -11208,18 +11202,18 @@
           <t>Additional hardening check #265</t>
         </is>
       </c>
-      <c r="F268" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G268" s="9" t="inlineStr">
+      <c r="F268" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H268" s="3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -11248,18 +11242,18 @@
           <t>Additional hardening check #266</t>
         </is>
       </c>
-      <c r="F269" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G269" s="9" t="inlineStr">
+      <c r="F269" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G269" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H269" s="3" t="n">
-        <v>150</v>
+        <v>205</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -11288,18 +11282,18 @@
           <t>Additional hardening check #267</t>
         </is>
       </c>
-      <c r="F270" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G270" s="9" t="inlineStr">
+      <c r="F270" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G270" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H270" s="3" t="n">
-        <v>167</v>
+        <v>215</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -11328,18 +11322,18 @@
           <t>Additional hardening check #268</t>
         </is>
       </c>
-      <c r="F271" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G271" s="9" t="inlineStr">
+      <c r="F271" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G271" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H271" s="3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -11368,18 +11362,18 @@
           <t>Additional hardening check #269</t>
         </is>
       </c>
-      <c r="F272" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G272" s="9" t="inlineStr">
+      <c r="F272" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G272" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H272" s="3" t="n">
-        <v>281</v>
+        <v>78</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -11408,18 +11402,18 @@
           <t>Additional hardening check #270</t>
         </is>
       </c>
-      <c r="F273" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G273" s="9" t="inlineStr">
+      <c r="F273" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G273" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H273" s="3" t="n">
-        <v>245</v>
+        <v>216</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -11448,18 +11442,18 @@
           <t>Additional hardening check #271</t>
         </is>
       </c>
-      <c r="F274" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G274" s="9" t="inlineStr">
+      <c r="F274" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G274" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H274" s="3" t="n">
-        <v>28</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -11488,18 +11482,18 @@
           <t>Additional hardening check #272</t>
         </is>
       </c>
-      <c r="F275" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G275" s="9" t="inlineStr">
+      <c r="F275" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G275" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H275" s="3" t="n">
-        <v>154</v>
+        <v>256</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -11528,18 +11522,18 @@
           <t>Additional hardening check #273</t>
         </is>
       </c>
-      <c r="F276" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G276" s="9" t="inlineStr">
+      <c r="F276" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G276" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H276" s="3" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -11568,18 +11562,18 @@
           <t>Additional hardening check #274</t>
         </is>
       </c>
-      <c r="F277" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr">
+      <c r="F277" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G277" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H277" s="3" t="n">
-        <v>207</v>
+        <v>98</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -11608,18 +11602,18 @@
           <t>Additional hardening check #275</t>
         </is>
       </c>
-      <c r="F278" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G278" s="9" t="inlineStr">
+      <c r="F278" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G278" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H278" s="3" t="n">
-        <v>67</v>
+        <v>193</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -11648,18 +11642,18 @@
           <t>Additional hardening check #276</t>
         </is>
       </c>
-      <c r="F279" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G279" s="9" t="inlineStr">
+      <c r="F279" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G279" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H279" s="3" t="n">
-        <v>49</v>
+        <v>268</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -11688,18 +11682,18 @@
           <t>Additional hardening check #277</t>
         </is>
       </c>
-      <c r="F280" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G280" s="9" t="inlineStr">
+      <c r="F280" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G280" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H280" s="3" t="n">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -11728,18 +11722,18 @@
           <t>Additional hardening check #278</t>
         </is>
       </c>
-      <c r="F281" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G281" s="9" t="inlineStr">
+      <c r="F281" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G281" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H281" s="3" t="n">
-        <v>116</v>
+        <v>259</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -11768,18 +11762,18 @@
           <t>Additional hardening check #279</t>
         </is>
       </c>
-      <c r="F282" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G282" s="9" t="inlineStr">
+      <c r="F282" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G282" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H282" s="3" t="n">
-        <v>290</v>
+        <v>65</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -11808,18 +11802,18 @@
           <t>Additional hardening check #280</t>
         </is>
       </c>
-      <c r="F283" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G283" s="9" t="inlineStr">
+      <c r="F283" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G283" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H283" s="3" t="n">
-        <v>275</v>
+        <v>256</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -11848,18 +11842,18 @@
           <t>Additional hardening check #281</t>
         </is>
       </c>
-      <c r="F284" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G284" s="9" t="inlineStr">
+      <c r="F284" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G284" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H284" s="3" t="n">
-        <v>264</v>
+        <v>73</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -11888,18 +11882,18 @@
           <t>Additional hardening check #282</t>
         </is>
       </c>
-      <c r="F285" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G285" s="9" t="inlineStr">
+      <c r="F285" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G285" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H285" s="3" t="n">
-        <v>197</v>
+        <v>128</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -11928,18 +11922,18 @@
           <t>Additional hardening check #283</t>
         </is>
       </c>
-      <c r="F286" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G286" s="9" t="inlineStr">
+      <c r="F286" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G286" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H286" s="3" t="n">
-        <v>203</v>
+        <v>281</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -11968,18 +11962,18 @@
           <t>Additional hardening check #284</t>
         </is>
       </c>
-      <c r="F287" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G287" s="9" t="inlineStr">
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G287" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H287" s="3" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -12008,18 +12002,18 @@
           <t>Additional hardening check #285</t>
         </is>
       </c>
-      <c r="F288" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G288" s="9" t="inlineStr">
+      <c r="F288" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G288" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H288" s="3" t="n">
-        <v>153</v>
+        <v>181</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -12048,18 +12042,18 @@
           <t>Additional hardening check #286</t>
         </is>
       </c>
-      <c r="F289" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G289" s="9" t="inlineStr">
+      <c r="F289" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G289" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H289" s="3" t="n">
-        <v>172</v>
+        <v>250</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -12088,18 +12082,18 @@
           <t>Additional hardening check #287</t>
         </is>
       </c>
-      <c r="F290" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G290" s="9" t="inlineStr">
+      <c r="F290" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G290" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H290" s="3" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -12128,18 +12122,18 @@
           <t>Additional hardening check #288</t>
         </is>
       </c>
-      <c r="F291" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G291" s="9" t="inlineStr">
+      <c r="F291" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G291" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H291" s="3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -12168,18 +12162,18 @@
           <t>Additional hardening check #289</t>
         </is>
       </c>
-      <c r="F292" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G292" s="9" t="inlineStr">
+      <c r="F292" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G292" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H292" s="3" t="n">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -12208,18 +12202,18 @@
           <t>Additional hardening check #290</t>
         </is>
       </c>
-      <c r="F293" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G293" s="9" t="inlineStr">
+      <c r="F293" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G293" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H293" s="3" t="n">
-        <v>117</v>
+        <v>28</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -12248,18 +12242,18 @@
           <t>Additional hardening check #291</t>
         </is>
       </c>
-      <c r="F294" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G294" s="9" t="inlineStr">
+      <c r="F294" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G294" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H294" s="3" t="n">
-        <v>260</v>
+        <v>166</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -12288,18 +12282,18 @@
           <t>Additional hardening check #292</t>
         </is>
       </c>
-      <c r="F295" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G295" s="9" t="inlineStr">
+      <c r="F295" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G295" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H295" s="3" t="n">
-        <v>144</v>
+        <v>262</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -12328,18 +12322,18 @@
           <t>Additional hardening check #293</t>
         </is>
       </c>
-      <c r="F296" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G296" s="9" t="inlineStr">
+      <c r="F296" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G296" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H296" s="3" t="n">
-        <v>81</v>
+        <v>226</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -12368,18 +12362,18 @@
           <t>Additional hardening check #294</t>
         </is>
       </c>
-      <c r="F297" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G297" s="9" t="inlineStr">
+      <c r="F297" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G297" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H297" s="3" t="n">
-        <v>62</v>
+        <v>251</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -12408,18 +12402,18 @@
           <t>Additional hardening check #295</t>
         </is>
       </c>
-      <c r="F298" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G298" s="9" t="inlineStr">
+      <c r="F298" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G298" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H298" s="3" t="n">
-        <v>146</v>
+        <v>69</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -12448,18 +12442,18 @@
           <t>Additional hardening check #296</t>
         </is>
       </c>
-      <c r="F299" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G299" s="9" t="inlineStr">
+      <c r="F299" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G299" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H299" s="3" t="n">
-        <v>131</v>
+        <v>187</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -12488,18 +12482,18 @@
           <t>Additional hardening check #297</t>
         </is>
       </c>
-      <c r="F300" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G300" s="9" t="inlineStr">
+      <c r="F300" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G300" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H300" s="3" t="n">
-        <v>75</v>
+        <v>210</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -12528,18 +12522,18 @@
           <t>Additional hardening check #298</t>
         </is>
       </c>
-      <c r="F301" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G301" s="9" t="inlineStr">
+      <c r="F301" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G301" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H301" s="3" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -12568,18 +12562,18 @@
           <t>Additional hardening check #299</t>
         </is>
       </c>
-      <c r="F302" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G302" s="9" t="inlineStr">
+      <c r="F302" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G302" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H302" s="3" t="n">
-        <v>220</v>
+        <v>80</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -12608,18 +12602,18 @@
           <t>Additional hardening check #300</t>
         </is>
       </c>
-      <c r="F303" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G303" s="9" t="inlineStr">
+      <c r="F303" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G303" s="7" t="inlineStr">
         <is>
           <t>PASS — Not Vulnerable</t>
         </is>
       </c>
       <c r="H303" s="3" t="n">
-        <v>34</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -12682,7 +12676,7 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -12692,7 +12686,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12702,14 +12696,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>main.py:193</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>/chat</t>
         </is>
@@ -12719,7 +12713,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12729,14 +12723,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>main.py:197</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>/predict</t>
         </is>
@@ -12746,7 +12740,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12756,14 +12750,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>main.py:201</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>/similar-markets</t>
         </is>
@@ -12773,7 +12767,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12783,14 +12777,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>main.py:208</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>/market-data</t>
         </is>
@@ -12800,7 +12794,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12810,14 +12804,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>main.py:212</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>/meta-data</t>
         </is>
@@ -12827,7 +12821,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12837,14 +12831,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>main.py:258</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>/meta-data-filtered</t>
         </is>
@@ -12854,7 +12848,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12864,14 +12858,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>main.py:262</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>/dashboard-summary</t>
         </is>
@@ -12881,7 +12875,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12891,14 +12885,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>main.py:273</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>/send-otp</t>
         </is>
@@ -12908,7 +12902,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12918,14 +12912,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>main.py:336</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>/verify-otp</t>
         </is>
@@ -12935,7 +12929,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12945,14 +12939,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>main.py:538</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>/save-profile</t>
         </is>
@@ -12962,7 +12956,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12972,14 +12966,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>main.py:548</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>/get-profile</t>
         </is>
@@ -12989,7 +12983,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -12999,14 +12993,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>main.py:586</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>/apply-scheme</t>
         </is>
@@ -13016,7 +13010,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -13026,14 +13020,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>main.py:610</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>/get-schemes</t>
         </is>
@@ -13043,7 +13037,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -13053,14 +13047,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>main.py:633</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>/save-mandi-prices</t>
         </is>
@@ -13070,7 +13064,7 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -13080,14 +13074,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>main.py:652</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>/docs</t>
         </is>
@@ -13097,7 +13091,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -13107,14 +13101,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>FastAPI built-in</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>/openapi.json</t>
         </is>
@@ -13124,7 +13118,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>❌ None</t>
         </is>
@@ -13134,7 +13128,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>FastAPI built-in</t>
         </is>
@@ -13206,7 +13200,7 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>fastapi</t>
         </is>
@@ -13221,12 +13215,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13238,7 +13232,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>uvicorn</t>
         </is>
@@ -13253,12 +13247,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13270,7 +13264,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>pydantic</t>
         </is>
@@ -13285,12 +13279,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13302,7 +13296,7 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>psycopg2</t>
         </is>
@@ -13317,12 +13311,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13334,7 +13328,7 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>pandas</t>
         </is>
@@ -13349,12 +13343,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13366,7 +13360,7 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>scikit-learn</t>
         </is>
@@ -13381,12 +13375,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13398,7 +13392,7 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>numpy</t>
         </is>
@@ -13413,12 +13407,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>No known CVEs</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -13430,7 +13424,7 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>random (stdlib)</t>
         </is>
@@ -13445,12 +13439,12 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Not a CSPRNG — use secrets module</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -13462,7 +13456,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>vite</t>
         </is>
@@ -13477,12 +13471,12 @@
           <t>Node</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Outdated — current is 5.x</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13494,7 +13488,7 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>selenium-webdriver</t>
         </is>
@@ -13509,7 +13503,7 @@
           <t>Node</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>3 high CVEs via glob@10.5.0</t>
         </is>
@@ -13526,7 +13520,7 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>glob</t>
         </is>
@@ -13541,7 +13535,7 @@
           <t>Node</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Widely publicized security vulns</t>
         </is>
@@ -13558,7 +13552,7 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>whatwg-encoding</t>
         </is>
@@ -13573,12 +13567,12 @@
           <t>Node</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Deprecated — use @exodus/bytes</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13590,7 +13584,7 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>.env (SMTP_PASSWORD)</t>
         </is>
@@ -13605,7 +13599,7 @@
           <t>Secret</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Gmail App Password in plaintext</t>
         </is>
@@ -13622,7 +13616,7 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>.env (BREVO_API_KEY)</t>
         </is>
@@ -13637,7 +13631,7 @@
           <t>Secret</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Live Brevo email API key in plaintext</t>
         </is>
@@ -13654,7 +13648,7 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>.env (SUPABASE_KEY)</t>
         </is>
@@ -13669,7 +13663,7 @@
           <t>Secret</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Supabase anon key in plaintext</t>
         </is>
@@ -13739,90 +13733,90 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>A01, A02, A07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>A01, A04, A05, A07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>A03, A05, A06, A09</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>A06, A08, A10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>OWASP Top 10 (2021)</t>
         </is>
@@ -13830,14 +13824,14 @@
     </row>
     <row r="10" ht="10" customHeight="1"/>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Overall Security Score</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>42 / 100 — Needs Critical Remediation Before Production</t>
         </is>
